--- a/codes/EMPIRE/Data handler/reduced/Generator.xlsx
+++ b/codes/EMPIRE/Data handler/reduced/Generator.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10609"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F53524-D1CB-CF43-8B42-174BCECBA6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35CC148-8510-0B4C-9976-E5FE380C4E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="17960" tabRatio="788" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="17960" tabRatio="788" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CapitalCosts" sheetId="15" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CapitalCosts!$A$1:$C$179</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">CO2Content!$A$1:$B$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">CO2Content!$A$1:$B$254</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Efficiency!$A$2:$C$219</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FixedOMCosts!$A$1:$C$179</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">FuelCosts!$A$1:$C$227</definedName>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="94">
   <si>
     <t>Source: PRIMES 2018</t>
   </si>
@@ -344,12 +344,6 @@
     <t>generatorLifetime</t>
   </si>
   <si>
-    <t>Wind offshore grounded</t>
-  </si>
-  <si>
-    <t>Wind offshore floating</t>
-  </si>
-  <si>
     <t>From TIMES</t>
   </si>
   <si>
@@ -367,9 +361,6 @@
       </rPr>
       <t>OFFSHORE WIND VISION FOR 2050</t>
     </r>
-  </si>
-  <si>
-    <t>Wind_offshr_grounded</t>
   </si>
   <si>
     <r>
@@ -393,6 +384,12 @@
       </rPr>
       <t xml:space="preserve"> Germany &amp; Denmark capacities here are for the Baltic projects</t>
     </r>
+  </si>
+  <si>
+    <t>Wind offshore</t>
+  </si>
+  <si>
+    <t>Wind_offshr</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1102,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -1336,7 +1333,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B44">
         <v>2</v>
@@ -1567,7 +1564,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B65">
         <v>3</v>
@@ -1798,7 +1795,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B86">
         <v>4</v>
@@ -2029,7 +2026,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B107">
         <v>5</v>
@@ -2260,7 +2257,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B128">
         <v>6</v>
@@ -2491,7 +2488,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B149">
         <v>7</v>
@@ -2722,7 +2719,7 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B170">
         <v>8</v>
@@ -2831,92 +2828,28 @@
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A180" t="s">
-        <v>89</v>
-      </c>
-      <c r="B180">
-        <v>1</v>
-      </c>
-      <c r="C180" s="18">
-        <v>4244.1666666666661</v>
-      </c>
+      <c r="C180" s="18"/>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A181" t="s">
-        <v>89</v>
-      </c>
-      <c r="B181">
-        <v>2</v>
-      </c>
-      <c r="C181" s="18">
-        <v>3472.5</v>
-      </c>
+      <c r="C181" s="18"/>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
-        <v>89</v>
-      </c>
-      <c r="B182">
-        <v>3</v>
-      </c>
-      <c r="C182" s="18">
-        <v>2539.52</v>
-      </c>
+      <c r="C182" s="18"/>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A183" t="s">
-        <v>89</v>
-      </c>
-      <c r="B183">
-        <v>4</v>
-      </c>
-      <c r="C183" s="18">
-        <v>2503.1111111111113</v>
-      </c>
+      <c r="C183" s="18"/>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A184" t="s">
-        <v>89</v>
-      </c>
-      <c r="B184">
-        <v>5</v>
-      </c>
-      <c r="C184" s="18">
-        <v>2314.7999999999997</v>
-      </c>
+      <c r="C184" s="18"/>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A185" t="s">
-        <v>89</v>
-      </c>
-      <c r="B185">
-        <v>6</v>
-      </c>
-      <c r="C185" s="18">
-        <v>2284.3421052631579</v>
-      </c>
+      <c r="C185" s="18"/>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A186" t="s">
-        <v>89</v>
-      </c>
-      <c r="B186">
-        <v>7</v>
-      </c>
-      <c r="C186" s="18">
-        <v>2239.3421052631579</v>
-      </c>
+      <c r="C186" s="18"/>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A187" t="s">
-        <v>89</v>
-      </c>
-      <c r="B187">
-        <v>8</v>
-      </c>
-      <c r="C187" s="18">
-        <v>2239.3421052631579</v>
-      </c>
+      <c r="C187" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C179" xr:uid="{7C2F75F1-22D4-4B25-877D-02FDA8CF96F6}"/>
@@ -3692,7 +3625,7 @@
       </c>
       <c r="E4" s="12"/>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -4120,7 +4053,7 @@
         <v>11582.579999999996</v>
       </c>
       <c r="E41" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -4444,7 +4377,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -4631,7 +4564,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -4639,7 +4572,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -4647,15 +4580,15 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B27">
         <v>0.8</v>
@@ -4663,7 +4596,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B28">
         <v>0.8</v>
@@ -4671,25 +4604,17 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B29">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B30">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31">
         <v>0.95</v>
       </c>
     </row>
@@ -4701,7 +4626,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -4936,7 +4861,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -4944,7 +4869,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -4952,22 +4877,14 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31">
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B255" xr:uid="{44FB08DB-D0F4-44C5-9830-AEB764E34A94}"/>
+  <autoFilter ref="A1:B254" xr:uid="{44FB08DB-D0F4-44C5-9830-AEB764E34A94}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4975,7 +4892,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F485F6EA-43A1-45AD-AE0E-6186EC1FBAD3}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -5162,7 +5079,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B24">
         <v>25</v>
@@ -5170,7 +5087,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="B25">
         <v>25</v>
@@ -5178,15 +5095,15 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B26">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B27">
         <v>40</v>
@@ -5194,7 +5111,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B28">
         <v>40</v>
@@ -5202,25 +5119,17 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B29">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B30">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31">
         <v>20</v>
       </c>
     </row>
@@ -5472,7 +5381,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -5703,7 +5612,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B44">
         <v>2</v>
@@ -5934,7 +5843,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B65">
         <v>3</v>
@@ -6165,7 +6074,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B86">
         <v>4</v>
@@ -6396,7 +6305,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B107">
         <v>5</v>
@@ -6627,7 +6536,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B128">
         <v>6</v>
@@ -6858,7 +6767,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B149">
         <v>7</v>
@@ -7089,7 +6998,7 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B170">
         <v>8</v>
@@ -7198,92 +7107,28 @@
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A180" t="s">
-        <v>89</v>
-      </c>
-      <c r="B180">
-        <v>1</v>
-      </c>
-      <c r="C180" s="18">
-        <v>64.166666666666657</v>
-      </c>
+      <c r="C180" s="18"/>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A181" t="s">
-        <v>89</v>
-      </c>
-      <c r="B181">
-        <v>2</v>
-      </c>
-      <c r="C181" s="18">
-        <v>52.5</v>
-      </c>
+      <c r="C181" s="18"/>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
-        <v>89</v>
-      </c>
-      <c r="B182">
-        <v>3</v>
-      </c>
-      <c r="C182" s="18">
-        <v>38.44</v>
-      </c>
+      <c r="C182" s="18"/>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A183" t="s">
-        <v>89</v>
-      </c>
-      <c r="B183">
-        <v>4</v>
-      </c>
-      <c r="C183" s="18">
-        <v>37.888888888888893</v>
-      </c>
+      <c r="C183" s="18"/>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A184" t="s">
-        <v>89</v>
-      </c>
-      <c r="B184">
-        <v>5</v>
-      </c>
-      <c r="C184" s="18">
-        <v>34.799999999999997</v>
-      </c>
+      <c r="C184" s="18"/>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A185" t="s">
-        <v>89</v>
-      </c>
-      <c r="B185">
-        <v>6</v>
-      </c>
-      <c r="C185" s="18">
-        <v>34.34210526315789</v>
-      </c>
+      <c r="C185" s="18"/>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A186" t="s">
-        <v>89</v>
-      </c>
-      <c r="B186">
-        <v>7</v>
-      </c>
-      <c r="C186" s="18">
-        <v>33.157894736842103</v>
-      </c>
+      <c r="C186" s="18"/>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A187" t="s">
-        <v>89</v>
-      </c>
-      <c r="B187">
-        <v>8</v>
-      </c>
-      <c r="C187" s="18">
-        <v>33.157894736842103</v>
-      </c>
+      <c r="C187" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C179" xr:uid="{1E2D1989-654C-4808-9318-DD8832D8C16A}"/>
@@ -7294,7 +7139,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86AA0E55-8A35-4D2F-9D77-EA22D2B08DB5}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -7513,7 +7358,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B28">
         <v>0.39</v>
@@ -7521,25 +7366,17 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="B29">
-        <v>0.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31">
         <v>0.82</v>
       </c>
     </row>
@@ -7551,7 +7388,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D299535-8217-4FDD-9775-08DFF4D5C579}">
-  <dimension ref="A1:C227"/>
+  <dimension ref="A1:C219"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.5" customWidth="1"/>
@@ -7846,7 +7683,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -8132,7 +7969,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -8418,7 +8255,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B80">
         <v>3</v>
@@ -8704,7 +8541,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B106">
         <v>4</v>
@@ -8990,7 +8827,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B132">
         <v>5</v>
@@ -9276,7 +9113,7 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B158">
         <v>6</v>
@@ -9562,7 +9399,7 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B184">
         <v>7</v>
@@ -9848,7 +9685,7 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B210">
         <v>8</v>
@@ -9953,94 +9790,6 @@
         <v>8</v>
       </c>
       <c r="C219">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A220" t="s">
-        <v>89</v>
-      </c>
-      <c r="B220">
-        <v>1</v>
-      </c>
-      <c r="C220">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A221" t="s">
-        <v>89</v>
-      </c>
-      <c r="B221">
-        <v>2</v>
-      </c>
-      <c r="C221">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A222" t="s">
-        <v>89</v>
-      </c>
-      <c r="B222">
-        <v>3</v>
-      </c>
-      <c r="C222">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A223" t="s">
-        <v>89</v>
-      </c>
-      <c r="B223">
-        <v>4</v>
-      </c>
-      <c r="C223">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A224" t="s">
-        <v>89</v>
-      </c>
-      <c r="B224">
-        <v>5</v>
-      </c>
-      <c r="C224">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A225" t="s">
-        <v>89</v>
-      </c>
-      <c r="B225">
-        <v>6</v>
-      </c>
-      <c r="C225">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A226" t="s">
-        <v>89</v>
-      </c>
-      <c r="B226">
-        <v>7</v>
-      </c>
-      <c r="C226">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A227" t="s">
-        <v>89</v>
-      </c>
-      <c r="B227">
-        <v>8</v>
-      </c>
-      <c r="C227">
         <v>0</v>
       </c>
     </row>
@@ -10150,7 +9899,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEFEB00D-6958-4463-84DB-BA9095D2D9BC}">
-  <dimension ref="A1:C227"/>
+  <dimension ref="A1:C219"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.33203125" customWidth="1"/>
@@ -12293,7 +12042,7 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -12304,7 +12053,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B197">
         <v>2</v>
@@ -12315,7 +12064,7 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B198">
         <v>3</v>
@@ -12326,7 +12075,7 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B199">
         <v>4</v>
@@ -12337,7 +12086,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B200">
         <v>5</v>
@@ -12348,7 +12097,7 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B201">
         <v>6</v>
@@ -12359,7 +12108,7 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B202">
         <v>7</v>
@@ -12370,7 +12119,7 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B203">
         <v>8</v>
@@ -12553,94 +12302,6 @@
       </c>
       <c r="C219">
         <v>0.34</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A220" t="s">
-        <v>89</v>
-      </c>
-      <c r="B220">
-        <v>1</v>
-      </c>
-      <c r="C220">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A221" t="s">
-        <v>89</v>
-      </c>
-      <c r="B221">
-        <v>2</v>
-      </c>
-      <c r="C221">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A222" t="s">
-        <v>89</v>
-      </c>
-      <c r="B222">
-        <v>3</v>
-      </c>
-      <c r="C222">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A223" t="s">
-        <v>89</v>
-      </c>
-      <c r="B223">
-        <v>4</v>
-      </c>
-      <c r="C223">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A224" t="s">
-        <v>89</v>
-      </c>
-      <c r="B224">
-        <v>5</v>
-      </c>
-      <c r="C224">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A225" t="s">
-        <v>89</v>
-      </c>
-      <c r="B225">
-        <v>6</v>
-      </c>
-      <c r="C225">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A226" t="s">
-        <v>89</v>
-      </c>
-      <c r="B226">
-        <v>7</v>
-      </c>
-      <c r="C226">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A227" t="s">
-        <v>89</v>
-      </c>
-      <c r="B227">
-        <v>8</v>
-      </c>
-      <c r="C227">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -12669,7 +12330,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -12690,7 +12351,7 @@
       </c>
       <c r="E3" s="19"/>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -12831,7 +12492,7 @@
         <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C15">
         <v>2260.2599999999998</v>
@@ -12939,7 +12600,7 @@
         <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C24">
         <v>2305</v>
@@ -13091,26 +12752,10 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>47</v>
-      </c>
-      <c r="B37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
+      <c r="C37"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
+      <c r="C38"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C38" xr:uid="{BF57B14D-7BEE-477E-9F48-7CE3A3F9031B}"/>
@@ -13600,7 +13245,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B35">
         <v>6</v>
@@ -13717,7 +13362,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B44">
         <v>7</v>
@@ -13834,7 +13479,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B53">
         <v>8</v>
@@ -13855,37 +13500,13 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>89</v>
-      </c>
-      <c r="B55">
-        <v>6</v>
-      </c>
-      <c r="C55" s="2">
-        <v>1</v>
-      </c>
+      <c r="C55" s="2"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>89</v>
-      </c>
-      <c r="B56">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2">
-        <v>1</v>
-      </c>
+      <c r="C56" s="2"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>89</v>
-      </c>
-      <c r="B57">
-        <v>8</v>
-      </c>
-      <c r="C57" s="2">
-        <v>1</v>
-      </c>
+      <c r="C57" s="2"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C58" s="2"/>
@@ -14532,6 +14153,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="d8af0d66-b3db-4c81-87bc-15f9b72a49e2">
@@ -14540,15 +14170,6 @@
     <TaxCatchAll xmlns="c1406b29-91bf-464c-9cd2-26ba5eb06139" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14571,6 +14192,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7204C7-40B5-4FE8-B1A1-A7F0C63B03D2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1CDE1F9-D70D-404B-AB05-C44B6E2BDE51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -14579,12 +14208,4 @@
     <ds:schemaRef ds:uri="c1406b29-91bf-464c-9cd2-26ba5eb06139"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7204C7-40B5-4FE8-B1A1-A7F0C63B03D2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>